--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-labresult.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-labresult.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2509" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2508" uniqueCount="431">
   <si>
     <t>Property</t>
   </si>
@@ -603,13 +603,7 @@
     <t>これは、検索、並べ替え、および表示の目的で使用される。</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>診断サービスセクションのコード。 / Codes for diagnostic service sections.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:$this}
@@ -848,9 +842,6 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
-  </si>
-  <si>
     <t>DiagnosticReport.category:first.id</t>
   </si>
   <si>
@@ -1083,7 +1074,7 @@
 Period</t>
   </si>
   <si>
-    <t>診断レポートの作成日時</t>
+    <t>診断レポートの対象となる検査・処置が実施された日時</t>
   </si>
   <si>
     <t>診断手順が患者に対して実行された場合、これは実施された時刻。対象が検体である場合は、検体採取時間から診断関連時刻を導き出すことができるが、検体情報が常に入手できるとは限らず、検体と診断関連時刻の正確な関係は必ずしも自明ではない。  
@@ -1365,6 +1356,9 @@
   </si>
   <si>
     <t>診断レポートの要約結論（解釈、インプレッション）を表すコード</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>レポートの補助として提供される診断コード。 / Diagnosis codes provided as adjuncts to the report.</t>
@@ -3300,26 +3294,24 @@
         <v>81</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="Y14" s="2"/>
+      <c r="Z14" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="AA14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB14" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>180</v>
@@ -3340,21 +3332,21 @@
         <v>81</v>
       </c>
       <c r="AL14" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>192</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3377,13 +3369,13 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3434,7 +3426,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3455,7 +3447,7 @@
         <v>81</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>81</v>
@@ -3463,10 +3455,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3495,7 +3487,7 @@
         <v>138</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>140</v>
@@ -3536,19 +3528,19 @@
         <v>81</v>
       </c>
       <c r="AB16" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3569,7 +3561,7 @@
         <v>81</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>81</v>
@@ -3577,10 +3569,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3603,19 +3595,19 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -3664,7 +3656,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3682,10 +3674,10 @@
         <v>81</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>81</v>
@@ -3693,10 +3685,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3719,13 +3711,13 @@
         <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3776,7 +3768,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3797,7 +3789,7 @@
         <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>81</v>
@@ -3805,10 +3797,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3837,7 +3829,7 @@
         <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>140</v>
@@ -3878,19 +3870,19 @@
         <v>81</v>
       </c>
       <c r="AB19" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AF19" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3911,7 +3903,7 @@
         <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>81</v>
@@ -3919,10 +3911,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3948,16 +3940,16 @@
         <v>105</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -4006,7 +3998,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4024,10 +4016,10 @@
         <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>81</v>
@@ -4035,10 +4027,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4061,16 +4053,16 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4120,7 +4112,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4138,10 +4130,10 @@
         <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>81</v>
@@ -4149,10 +4141,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4178,14 +4170,14 @@
         <v>111</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -4234,7 +4226,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4252,10 +4244,10 @@
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>81</v>
@@ -4263,10 +4255,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4289,17 +4281,17 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -4348,7 +4340,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4366,10 +4358,10 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>81</v>
@@ -4377,10 +4369,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4403,19 +4395,19 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4464,7 +4456,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4482,10 +4474,10 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>81</v>
@@ -4493,10 +4485,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4519,19 +4511,19 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -4580,7 +4572,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4598,10 +4590,10 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
@@ -4609,13 +4601,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>180</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>181</v>
@@ -4640,13 +4632,13 @@
         <v>182</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4657,7 +4649,7 @@
         <v>81</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>81</v>
@@ -4676,7 +4668,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>263</v>
+        <v>185</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -4712,21 +4704,21 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>192</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4749,13 +4741,13 @@
         <v>81</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4806,7 +4798,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4827,7 +4819,7 @@
         <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>81</v>
@@ -4835,10 +4827,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4867,7 +4859,7 @@
         <v>138</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>140</v>
@@ -4908,19 +4900,19 @@
         <v>81</v>
       </c>
       <c r="AB28" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4941,7 +4933,7 @@
         <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
@@ -4949,10 +4941,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4975,19 +4967,19 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -5036,7 +5028,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5054,10 +5046,10 @@
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
@@ -5065,10 +5057,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5091,13 +5083,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5148,7 +5140,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5169,7 +5161,7 @@
         <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>81</v>
@@ -5177,10 +5169,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5209,7 +5201,7 @@
         <v>138</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>140</v>
@@ -5250,19 +5242,19 @@
         <v>81</v>
       </c>
       <c r="AB31" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5283,7 +5275,7 @@
         <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
@@ -5291,10 +5283,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5320,16 +5312,16 @@
         <v>105</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="O32" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>81</v>
@@ -5378,7 +5370,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5396,10 +5388,10 @@
         <v>81</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>81</v>
@@ -5407,10 +5399,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5433,16 +5425,16 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5492,7 +5484,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5510,10 +5502,10 @@
         <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>81</v>
@@ -5521,10 +5513,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5550,14 +5542,14 @@
         <v>111</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
@@ -5606,7 +5598,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5624,10 +5616,10 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
@@ -5635,10 +5627,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5661,17 +5653,17 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -5720,7 +5712,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5738,10 +5730,10 @@
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
@@ -5749,10 +5741,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5775,19 +5767,19 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -5836,7 +5828,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5854,10 +5846,10 @@
         <v>81</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
@@ -5865,10 +5857,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5891,19 +5883,19 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -5952,7 +5944,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5970,10 +5962,10 @@
         <v>81</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>81</v>
@@ -5981,14 +5973,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6010,10 +6002,10 @@
         <v>182</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6044,7 +6036,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -6062,7 +6054,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>91</v>
@@ -6077,24 +6069,24 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>282</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6117,13 +6109,13 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6174,7 +6166,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6195,7 +6187,7 @@
         <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>81</v>
@@ -6203,10 +6195,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6235,7 +6227,7 @@
         <v>138</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>140</v>
@@ -6276,19 +6268,19 @@
         <v>81</v>
       </c>
       <c r="AB40" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6309,7 +6301,7 @@
         <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
@@ -6317,10 +6309,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6343,19 +6335,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6392,17 +6384,17 @@
         <v>81</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6420,10 +6412,10 @@
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>81</v>
@@ -6431,13 +6423,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>81</v>
@@ -6459,19 +6451,19 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -6481,7 +6473,7 @@
         <v>81</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>81</v>
@@ -6520,7 +6512,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6538,10 +6530,10 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
@@ -6549,10 +6541,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6575,13 +6567,13 @@
         <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6632,7 +6624,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6653,7 +6645,7 @@
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>81</v>
@@ -6661,10 +6653,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6693,7 +6685,7 @@
         <v>138</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>140</v>
@@ -6734,19 +6726,19 @@
         <v>81</v>
       </c>
       <c r="AB44" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6767,7 +6759,7 @@
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
@@ -6775,10 +6767,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6804,16 +6796,16 @@
         <v>105</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -6862,7 +6854,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6880,10 +6872,10 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -6891,10 +6883,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6917,16 +6909,16 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6976,7 +6968,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6994,10 +6986,10 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -7005,10 +6997,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7034,14 +7026,14 @@
         <v>111</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -7090,7 +7082,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7108,10 +7100,10 @@
         <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -7119,10 +7111,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7145,17 +7137,17 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7204,7 +7196,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7222,10 +7214,10 @@
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7233,10 +7225,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7259,19 +7251,19 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>81</v>
@@ -7320,7 +7312,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7338,10 +7330,10 @@
         <v>81</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
@@ -7349,10 +7341,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7375,19 +7367,19 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>81</v>
@@ -7436,7 +7428,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7454,10 +7446,10 @@
         <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
@@ -7465,14 +7457,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7491,19 +7483,19 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -7552,7 +7544,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7567,28 +7559,28 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>323</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7607,19 +7599,19 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="O52" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -7668,7 +7660,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7683,28 +7675,28 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>333</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7723,19 +7715,19 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="O53" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -7784,7 +7776,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7799,28 +7791,28 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>343</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7839,19 +7831,19 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="O54" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -7900,7 +7892,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7918,25 +7910,25 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7955,19 +7947,19 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="O55" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>81</v>
@@ -8016,7 +8008,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8031,28 +8023,28 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>362</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8071,19 +8063,19 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="O56" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8132,7 +8124,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8147,24 +8139,24 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>362</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8187,19 +8179,19 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="O57" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>81</v>
@@ -8248,7 +8240,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8266,10 +8258,10 @@
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>81</v>
@@ -8277,14 +8269,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8303,19 +8295,19 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -8364,7 +8356,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8382,10 +8374,10 @@
         <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -8393,10 +8385,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8419,16 +8411,16 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8478,7 +8470,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8499,7 +8491,7 @@
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>81</v>
@@ -8507,14 +8499,14 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8533,19 +8525,19 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="O60" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -8594,7 +8586,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8612,10 +8604,10 @@
         <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>81</v>
@@ -8623,10 +8615,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8649,13 +8641,13 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8706,7 +8698,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8727,7 +8719,7 @@
         <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>81</v>
@@ -8735,10 +8727,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8767,7 +8759,7 @@
         <v>138</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>140</v>
@@ -8820,7 +8812,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -8841,7 +8833,7 @@
         <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>81</v>
@@ -8849,14 +8841,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8878,10 +8870,10 @@
         <v>137</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>140</v>
@@ -8936,7 +8928,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -8965,10 +8957,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8991,19 +8983,19 @@
         <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="O64" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -9052,7 +9044,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9073,7 +9065,7 @@
         <v>81</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>81</v>
@@ -9081,10 +9073,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9107,16 +9099,16 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9166,7 +9158,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>91</v>
@@ -9187,7 +9179,7 @@
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
@@ -9195,14 +9187,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9221,19 +9213,19 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="O66" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>81</v>
@@ -9282,7 +9274,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9300,10 +9292,10 @@
         <v>81</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>81</v>
@@ -9311,10 +9303,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9340,13 +9332,13 @@
         <v>182</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9372,13 +9364,13 @@
         <v>81</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>185</v>
+        <v>421</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
@@ -9396,7 +9388,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9414,10 +9406,10 @@
         <v>81</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>81</v>
@@ -9425,10 +9417,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9451,19 +9443,19 @@
         <v>81</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>81</v>
@@ -9512,7 +9504,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9530,10 +9522,10 @@
         <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>81</v>
